--- a/InputData/elec/BBNPPTY/BAU Ban New Power Plants This Year.xlsx
+++ b/InputData/elec/BBNPPTY/BAU Ban New Power Plants This Year.xlsx
@@ -2989,4 +2989,175 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{971C8F4A-E10E-4C19-844B-3416D802FA23}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3F51D06-EFCE-4C0B-BB57-11FFF6362EB6}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAC2D09F-B9CA-4F44-B9DD-E131E48950C5}"/>
 </file>
--- a/InputData/elec/BBNPPTY/BAU Ban New Power Plants This Year.xlsx
+++ b/InputData/elec/BBNPPTY/BAU Ban New Power Plants This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Models\US\Models\eps-us\InputData\elec\BBNPPTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\South Korea\Models\eps-southkorea\InputData\elec\BBNPPTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED5C7C3-C6DD-4CC0-A75D-D5DA17DC76DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703EACAA-B4B9-4932-BFEF-1DCFA13430D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="38865" windowHeight="17235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6825" yWindow="4485" windowWidth="17280" windowHeight="10005" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Source:</t>
   </si>
@@ -141,6 +141,12 @@
   </si>
   <si>
     <t>and the construction time for new or modified plants.</t>
+  </si>
+  <si>
+    <t>2026-08-21 power-sector calibration (cal9): endogenous builds banned through 2030 for hard coal, lignite, nuclear, and SMR - lead-time convention (multi-year construction means nothing not already in the pipeline can come online before ~2030; the pipeline enters via the mandated schedule). Post-2030 the economic build channel reopens.</t>
+  </si>
+  <si>
+    <t>2026-09-04 start-year convention (matches eps-us, INITIAL TIME 2025 / vintages end 2024 / BPMCCS 2025 = first-year builds / BBNPPTY bans all sources through the last historical year): all sources banned from endogenous builds through 2025, the last year with actual installation data in BPMCCS (설비현황_19~25). Historical capacity therefore comes only from start-year vintages (through 2020) plus the mandated schedule. Lead-time bans for coal/lignite/nuclear/SMR through 2030 unchanged.</t>
   </si>
 </sst>
 </file>
@@ -523,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="60.85546875" customWidth="1"/>
@@ -590,6 +596,16 @@
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -719,16 +735,16 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="5">
         <v>1</v>
@@ -814,10 +830,10 @@
         <v>1</v>
       </c>
       <c r="E3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="5">
         <v>0</v>
@@ -909,10 +925,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="5">
         <v>0</v>
@@ -1004,25 +1020,25 @@
         <v>1</v>
       </c>
       <c r="E5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
         <v>0</v>
@@ -1099,10 +1115,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
@@ -1194,10 +1210,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
@@ -1289,10 +1305,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
@@ -1384,10 +1400,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
@@ -1479,10 +1495,10 @@
         <v>1</v>
       </c>
       <c r="E10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
@@ -1574,10 +1590,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="5">
         <v>0</v>
@@ -1669,10 +1685,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="5">
         <v>0</v>
@@ -1764,10 +1780,10 @@
         <v>1</v>
       </c>
       <c r="E13" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="5">
         <v>0</v>
@@ -1859,16 +1875,16 @@
         <v>1</v>
       </c>
       <c r="E14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="5">
         <v>1</v>
@@ -1954,10 +1970,10 @@
         <v>1</v>
       </c>
       <c r="E15" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="5">
         <v>0</v>
@@ -2049,10 +2065,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="5">
         <v>0</v>
@@ -2144,10 +2160,10 @@
         <v>1</v>
       </c>
       <c r="E17" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="5">
         <v>0</v>
@@ -2239,10 +2255,10 @@
         <v>1</v>
       </c>
       <c r="E18" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="5">
         <v>0</v>
@@ -2714,25 +2730,25 @@
         <v>1</v>
       </c>
       <c r="E23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="5">
         <v>0</v>
@@ -2809,10 +2825,10 @@
         <v>1</v>
       </c>
       <c r="E24" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="5">
         <v>0</v>
@@ -2904,10 +2920,10 @@
         <v>1</v>
       </c>
       <c r="E25" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="5">
         <v>0</v>
@@ -2992,6 +3008,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -3135,7 +3157,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3144,20 +3166,37 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{971C8F4A-E10E-4C19-844B-3416D802FA23}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAC2D09F-B9CA-4F44-B9DD-E131E48950C5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3F51D06-EFCE-4C0B-BB57-11FFF6362EB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{971C8F4A-E10E-4C19-844B-3416D802FA23}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAC2D09F-B9CA-4F44-B9DD-E131E48950C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3F51D06-EFCE-4C0B-BB57-11FFF6362EB6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>